--- a/src/data/raw/2015 შუალედური მაისი.xlsx
+++ b/src/data/raw/2015 შუალედური მაისი.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Election portal data sets\Election results\შედეგები\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Personal)\My projects\Elections\ge_elections_dashboard\wireframe\observable_framework\elections_data\src\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A777A3B7-F1F2-4DE4-805C-D4AC49C8BCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E9C57C-46F7-417A-9CC7-BE9057353603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1491" yWindow="540" windowWidth="28775" windowHeight="17254" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="64.13 ფოცხო" sheetId="4" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>ოლქის N და დასახელება</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>ვასილ გაბისონია</t>
+  </si>
+  <si>
+    <t>maj_id</t>
   </si>
 </sst>
 </file>
@@ -213,14 +216,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -539,233 +535,245 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.84375" customWidth="1"/>
-    <col min="3" max="3" width="10.4609375" customWidth="1"/>
-    <col min="4" max="4" width="20.07421875" customWidth="1"/>
-    <col min="5" max="5" width="22.3046875" customWidth="1"/>
-    <col min="6" max="6" width="12.53515625" customWidth="1"/>
-    <col min="7" max="7" width="12.84375" customWidth="1"/>
-    <col min="8" max="8" width="15.53515625" customWidth="1"/>
-    <col min="9" max="9" width="18.07421875" customWidth="1"/>
-    <col min="10" max="13" width="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="15.07421875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.84375" customWidth="1"/>
+    <col min="4" max="4" width="10.4609375" customWidth="1"/>
+    <col min="5" max="5" width="20.07421875" customWidth="1"/>
+    <col min="6" max="6" width="22.3046875" customWidth="1"/>
+    <col min="7" max="7" width="12.53515625" customWidth="1"/>
+    <col min="8" max="8" width="12.84375" customWidth="1"/>
+    <col min="9" max="9" width="15.53515625" customWidth="1"/>
+    <col min="10" max="10" width="18.07421875" customWidth="1"/>
+    <col min="11" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.3046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="47.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:16" ht="47.6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.9" x14ac:dyDescent="0.5">
-      <c r="A2" s="3">
+    <row r="2" spans="1:16" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="A2">
+        <v>6413</v>
+      </c>
+      <c r="B2" s="3">
         <v>64</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C2" s="1">
         <v>13</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>34</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>626</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>282</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>478</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>488</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>600</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>42</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>15</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>204</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>210</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>17</v>
       </c>
-      <c r="O2" s="7">
-        <f>N2*100/H2</f>
+      <c r="P2" s="7">
+        <f>O2*100/I2</f>
         <v>3.4836065573770494</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.9" x14ac:dyDescent="0.5">
-      <c r="A3" s="3">
+    <row r="3" spans="1:16" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="A3">
+        <v>6413</v>
+      </c>
+      <c r="B3" s="3">
         <v>64</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C3" s="1">
         <v>13</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>35</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>689</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>259</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>443</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>491</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>650</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>128</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>76</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>266</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>15</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>6</v>
       </c>
-      <c r="O3" s="7">
-        <f>N3*100/H3</f>
+      <c r="P3" s="7">
+        <f>O3*100/I3</f>
         <v>1.2219959266802445</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A4" s="1">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>6711</v>
+      </c>
+      <c r="B4" s="1">
         <v>67</v>
       </c>
-      <c r="B4" s="1">
+      <c r="C4" s="1">
         <v>11</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>45</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>1152</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>217</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>548</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>731</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>1100</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>4</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>305</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>410</v>
       </c>
-      <c r="N4" s="1">
+      <c r="O4" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A12" s="6"/>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B12" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
-    <cfRule type="expression" dxfId="6" priority="5">
-      <formula>$B2="ჯამი"</formula>
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>$C2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:L4">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>$C4="ჯამი"</formula>
+  <conditionalFormatting sqref="B4:M4 O4">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>$D4="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:N3 N4">
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>$C2="ჯამი"</formula>
+  <conditionalFormatting sqref="C2:O3">
+    <cfRule type="expression" dxfId="3" priority="6">
+      <formula>$D2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.17" right="0.17" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -775,10 +783,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46BEFDF-598D-4949-AE69-03E5187C8320}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="79.3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="79.3" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -791,8 +799,11 @@
       <c r="D1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.9" x14ac:dyDescent="0.5">
       <c r="A2" s="3">
         <v>64</v>
       </c>
@@ -805,8 +816,11 @@
       <c r="D2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="E2">
+        <v>6413</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.9" x14ac:dyDescent="0.5">
       <c r="A3" s="3">
         <v>64</v>
       </c>
@@ -819,8 +833,11 @@
       <c r="D3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="E3">
+        <v>6413</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.9" x14ac:dyDescent="0.5">
       <c r="A4" s="3">
         <v>64</v>
       </c>
@@ -833,8 +850,11 @@
       <c r="D4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="E4">
+        <v>6413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.9" x14ac:dyDescent="0.5">
       <c r="A5" s="3">
         <v>64</v>
       </c>
@@ -847,8 +867,11 @@
       <c r="D5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E5">
+        <v>6413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>67</v>
       </c>
@@ -861,8 +884,11 @@
       <c r="D6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E6">
+        <v>6711</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>67</v>
       </c>
@@ -875,8 +901,11 @@
       <c r="D7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E7">
+        <v>6711</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>67</v>
       </c>
@@ -889,25 +918,23 @@
       <c r="D8" t="s">
         <v>27</v>
       </c>
+      <c r="E8">
+        <v>6711</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A5">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$B2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B8">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$C3="ჯამი"</formula>
+  <conditionalFormatting sqref="A6:B8">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$C2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B5">
-    <cfRule type="expression" dxfId="1" priority="4">
-      <formula>$C2="ჯამი"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B6">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>$C2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
